--- a/productos/08-nomina-basica/Nomina-Basica.xlsx
+++ b/productos/08-nomina-basica/Nomina-Basica.xlsx
@@ -123,7 +123,7 @@
     <t xml:space="preserve">7. Celdas protegidas</t>
   </si>
   <si>
-    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Contraseña de desprotección: plantilla2026.</t>
+    <t xml:space="preserve">Las hojas están protegidas para que no borres fórmulas por accidente. Solo puedes escribir en las celdas resaltadas en color crema / texto azul. Si necesitas editar otra celda, ve a Revisar → Desproteger hoja (no pide contraseña).</t>
   </si>
   <si>
     <t xml:space="preserve">Nota</t>
@@ -1916,11 +1916,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="34242849"/>
-        <c:axId val="50341019"/>
+        <c:axId val="9820719"/>
+        <c:axId val="68472477"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="34242849"/>
+        <c:axId val="9820719"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1952,7 +1952,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="50341019"/>
+        <c:crossAx val="68472477"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1960,7 +1960,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="50341019"/>
+        <c:axId val="68472477"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2002,7 +2002,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="34242849"/>
+        <c:crossAx val="9820719"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2250,11 +2250,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="69497474"/>
-        <c:axId val="49143758"/>
+        <c:axId val="61137381"/>
+        <c:axId val="60973976"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="69497474"/>
+        <c:axId val="61137381"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2286,7 +2286,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49143758"/>
+        <c:crossAx val="60973976"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2294,7 +2294,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="49143758"/>
+        <c:axId val="60973976"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2336,7 +2336,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69497474"/>
+        <c:crossAx val="61137381"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2838,7 +2838,7 @@
       <c r="F24" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="16">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B4:F6"/>
@@ -2989,7 +2989,7 @@
       <c r="C28" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="18">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B4:C4"/>
@@ -3180,7 +3180,7 @@
       <c r="D17" s="20"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="B17:D17"/>
@@ -3367,7 +3367,7 @@
       <c r="E14" s="23"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
@@ -3815,7 +3815,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="2">
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A3:N3"/>
@@ -4470,7 +4470,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="4">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
@@ -4574,7 +4574,7 @@
       <c r="I7" s="40"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="true" password="ee36" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
+  <sheetProtection sheet="true" formatCells="false" formatColumns="false" formatRows="false" insertRows="false" selectLockedCells="true" selectUnlockedCells="true"/>
   <mergeCells count="10">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
